--- a/llmserver/excelsheets/PAYOOR_INGREDIENTS.xlsx
+++ b/llmserver/excelsheets/PAYOOR_INGREDIENTS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="75">
   <si>
     <t>Name</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Ofada sauce</t>
   </si>
   <si>
-    <t>Tomato, Locust Beans - Iru, Curry Powder - Durcos, Palm Oil - local, Salt - Mr chef, EGG,Onions - Red, Smoked panla - fish, Cow meat [boneless beef], Rice (long grain), Pepper - Ata Rodo, Garlic powder, Crayfish, Knorr Chicken Seasoning Cubes</t>
+    <t>Tomato, Locust Beans - Iru, Curry Powder - Durcos, Palm Oil - local, Salt - Mr chef, EGG,Onions - Red, Smoked panla - fish, Cow meat [boneless beef], Rice (long grain), Pepper - Ata Rodo, Garlic powder, Crayfish, Knorr Chicken Seasoning Cubes,Ponmo - meat [brown]</t>
   </si>
   <si>
     <t>1hr</t>
@@ -211,7 +211,31 @@
     <t xml:space="preserve">Ofé Nsala [White soup] </t>
   </si>
   <si>
-    <t xml:space="preserve"> Goat Meat,  Dry Smoked Catfish, Uziza Leaves, Uda seed [Negro pepper], Crayfish, Knorr Chicken Seasoning Cubes, Salt - Mr chef, Ginger powder, Garlic powder, Grinded cameroun pepper</t>
+    <t xml:space="preserve"> Goat Meat,  Dry Smoked Catfish, Uziza Leaves, Uda seed [Negro pepper], Crayfish, Knorr Chicken Seasoning Cubes, Salt - Mr chef, Ginger powder, Garlic powder, Grinded cameroun pepper,Onions - Red</t>
+  </si>
+  <si>
+    <t>Ofe Onugbu</t>
+  </si>
+  <si>
+    <t>cocoyam - Soup Thickener,Bitter leaf - chopped,Knorr Chicken Seasoning Cubes,Crayfish,Goat Meat,Stock fish - [Dice flesh],Ponmo - meat [brown],Pepper - Ata Rodo, Grinded cameroun pepper, ,Cow meat - beef,Palm Oil - Local,Salt - Mr chef,Onions - Red</t>
+  </si>
+  <si>
+    <t>Ikokore</t>
+  </si>
+  <si>
+    <t>Water yam,Palm Oil - Local,Salt - Mr chef,Ponmo - meat [brown],Sole Fish - Abo,Pepper - Ata Rodo,Pepper -Tatashe,smoked panla - fish,Onions - Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yam Porridge </t>
+  </si>
+  <si>
+    <t>Yam,Palm Oil - Local,Salt - Mr chef,Ponmo - meat [brown],Pepper - Ata Rodo,Pepper -Tatashe,smoked panla - fish,Tomato paste - Gino original,Grinded cameroun pepper,Onions - Red,Garlic powder,Maggi Star Tablet Chicken Flavour</t>
+  </si>
+  <si>
+    <t>Beans - oloyin</t>
+  </si>
+  <si>
+    <t>Beans,Palm Oil - Local,Salt - Mr chef,Pepper - Ata Rodo,Pepper -Tatashe,Tomato paste - Gino original,Grinded cameroun pepper,Onions - Red,Garlic powder,Maggi Star Tablet Chicken Flavour</t>
   </si>
 </sst>
 </file>
@@ -1091,32 +1115,48 @@
       <c r="F25" s="11"/>
     </row>
     <row r="26">
-      <c r="A26" s="12"/>
-      <c r="B26" s="6"/>
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27">
-      <c r="A27" s="13"/>
-      <c r="B27" s="10"/>
+      <c r="A27" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="11"/>
     </row>
     <row r="28">
-      <c r="A28" s="12"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="7"/>
     </row>
     <row r="29">
-      <c r="A29" s="13"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
